--- a/legislacao_vigente_animais_completa.xlsx
+++ b/legislacao_vigente_animais_completa.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1491,6 +1491,58 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>DL n.º 103/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Decreto-Lei n.º 103/2026, de 22 de maio</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>22 de Maio de 2026</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Controlos Oficiais</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Execução do Regulamento (UE) 2017/625</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>Assegura a execução nacional do Regulamento (UE) 2017/625 (controlos oficiais e outras atividades oficiais, incluindo bem-estar animal); DGAV autoridade competente; delegação de tarefas; deveres de colaboração dos operadores; taxas; contraordenações económicas (RJCE); revoga o DL 178/2008; em vigor desde 21.7.2026</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>Art. 3 (autoridade competente), 6 (delegação), 7 (deveres dos operadores), 9-12 (taxas), 13-16 (contraordenações)</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>Reg. (UE) 2017/625, DL 9/2021 (RJCE), Portaria 304-A/2026/1</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>Regime nacional dos controlos oficiais aplicável ao Regulamento (UE) 2026/1818 (considerandos 31 e 32; art. 4.º, al. u))</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
